--- a/data/trans_orig/P71_R2-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P71_R2-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según dificultad para llegar a fin de mes en 2007</t>
+          <t>Población según dificultad para llegar a fin de mes en 2007 (tasa de respuesta: 98,33%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>54144</t>
+          <t>53061</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>84643</t>
+          <t>84509</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,82 +748,82 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
+          <t>7,74%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>12,33%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>39231</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>29112</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>53450</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>5,78%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>4,29%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>7,87%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>107809</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>89613</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>128959</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
           <t>7,9%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>12,35%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>39231</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>28614</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>51983</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>5,78%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>4,21%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>7,66%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>107809</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>88586</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>129683</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>7,9%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,45%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>249791</t>
+          <t>249808</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>301742</t>
+          <t>302119</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>36,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>44,01%</t>
+          <t>44,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>215632</t>
+          <t>216003</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>265140</t>
+          <t>264359</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>31,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,05%</t>
+          <t>38,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>482419</t>
+          <t>479685</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>550850</t>
+          <t>553329</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>40,55%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>219545</t>
+          <t>216635</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>266691</t>
+          <t>266281</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>38,84%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>211739</t>
+          <t>212490</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>261427</t>
+          <t>260731</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>38,51%</t>
+          <t>38,4%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>447194</t>
+          <t>442304</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>514670</t>
+          <t>512855</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>32,41%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>37,58%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>82254</t>
+          <t>82842</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>119554</t>
+          <t>119751</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>141302</t>
+          <t>142535</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>185180</t>
+          <t>185126</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>235665</t>
+          <t>233075</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>293305</t>
+          <t>290758</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,31%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>126308</t>
+          <t>123975</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>172272</t>
+          <t>170202</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>78592</t>
+          <t>78038</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>116897</t>
+          <t>113959</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>215810</t>
+          <t>215689</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>274440</t>
+          <t>273253</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,4%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>286788</t>
+          <t>286635</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>348898</t>
+          <t>345626</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>36,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>269032</t>
+          <t>269737</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>328706</t>
+          <t>331439</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>34,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>577829</t>
+          <t>572088</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>658137</t>
+          <t>655166</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>34,52%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>294552</t>
+          <t>296527</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>354673</t>
+          <t>354443</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,82 +1543,82 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
+          <t>31,3%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>37,41%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>306410</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>276857</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>336673</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>32,24%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>29,13%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>35,43%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>589</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>631093</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>589912</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>675764</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>33,26%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
           <t>31,09%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>37,44%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>285</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>306410</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>278112</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>337213</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>32,24%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>29,27%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>35,49%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>589</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>631093</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>591229</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>671985</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>33,26%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>31,16%</t>
-        </is>
-      </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>35,61%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>133681</t>
+          <t>136600</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>184658</t>
+          <t>183634</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>221627</t>
+          <t>222076</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>278399</t>
+          <t>281405</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>372989</t>
+          <t>372894</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>446237</t>
+          <t>443565</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,37%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>65154</t>
+          <t>64966</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>99705</t>
+          <t>98737</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>48321</t>
+          <t>47251</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>74768</t>
+          <t>76379</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>119951</t>
+          <t>118906</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>164273</t>
+          <t>162278</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,1%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>216644</t>
+          <t>215738</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>267064</t>
+          <t>266523</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>39,68%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>154975</t>
+          <t>153225</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>200025</t>
+          <t>196943</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>383250</t>
+          <t>384060</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>450676</t>
+          <t>449927</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>33,56%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>192271</t>
+          <t>191928</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>243719</t>
+          <t>244248</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>36,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>201298</t>
+          <t>204097</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>249431</t>
+          <t>252545</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>37,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>413149</t>
+          <t>412558</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>482596</t>
+          <t>479029</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,0%</t>
+          <t>35,73%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>111459</t>
+          <t>110641</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>154110</t>
+          <t>154283</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>184003</t>
+          <t>182234</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>227763</t>
+          <t>227707</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>306037</t>
+          <t>306722</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>369671</t>
+          <t>371239</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,69%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>129549</t>
+          <t>129152</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>173472</t>
+          <t>172902</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>125663</t>
+          <t>124707</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>169623</t>
+          <t>168383</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>267306</t>
+          <t>267598</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>330315</t>
+          <t>329471</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>16,96%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>261710</t>
+          <t>263898</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>317105</t>
+          <t>319098</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>252492</t>
+          <t>251316</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>309017</t>
+          <t>308028</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>527366</t>
+          <t>531573</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>605019</t>
+          <t>608553</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>31,32%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>265195</t>
+          <t>265459</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>320967</t>
+          <t>320080</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>260313</t>
+          <t>261638</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>319816</t>
+          <t>320370</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>536626</t>
+          <t>540071</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>619048</t>
+          <t>618386</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>31,83%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>171054</t>
+          <t>170691</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>219673</t>
+          <t>220441</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>276746</t>
+          <t>273669</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>334698</t>
+          <t>333019</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>461047</t>
+          <t>461321</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>535285</t>
+          <t>533936</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,48%</t>
         </is>
       </c>
     </row>
@@ -3009,12 +3009,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>411386</t>
+          <t>411848</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>488922</t>
+          <t>492353</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>306911</t>
+          <t>304993</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>377855</t>
+          <t>376959</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>734726</t>
+          <t>734965</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>842184</t>
+          <t>841308</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,85%</t>
         </is>
       </c>
     </row>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1073923</t>
+          <t>1063806</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1181036</t>
+          <t>1177014</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,12 +3137,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>36,56%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>944363</t>
+          <t>940337</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1048545</t>
+          <t>1046412</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>31,57%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2037523</t>
+          <t>2044277</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2195403</t>
+          <t>2191729</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>31,23%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>33,48%</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1024300</t>
+          <t>1020437</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1135660</t>
+          <t>1134335</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,12 +3250,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>31,58%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>999325</t>
+          <t>1002253</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1109321</t>
+          <t>1112961</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2064885</t>
+          <t>2052357</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2223075</t>
+          <t>2208030</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>33,73%</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>536405</t>
+          <t>542936</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>626782</t>
+          <t>627470</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>873035</t>
+          <t>873730</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>977713</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1429935</t>
+          <t>1443179</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1569869</t>
+          <t>1577379</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>24,1%</t>
         </is>
       </c>
     </row>
@@ -3615,7 +3615,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según dificultad para llegar a fin de mes en 2012</t>
+          <t>Población según dificultad para llegar a fin de mes en 2012 (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3810,12 +3810,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>80579</t>
+          <t>78772</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>118355</t>
+          <t>118723</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3825,12 +3825,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3845,12 +3845,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>62621</t>
+          <t>63195</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>96817</t>
+          <t>97390</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3880,12 +3880,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>154284</t>
+          <t>155203</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>209711</t>
+          <t>209283</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>15,03%</t>
         </is>
       </c>
     </row>
@@ -3923,12 +3923,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>175215</t>
+          <t>173596</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>225558</t>
+          <t>222099</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3938,12 +3938,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3958,12 +3958,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>181702</t>
+          <t>179891</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>231479</t>
+          <t>229531</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,45%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>367637</t>
+          <t>369864</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>435442</t>
+          <t>435864</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>31,3%</t>
         </is>
       </c>
     </row>
@@ -4036,12 +4036,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>181718</t>
+          <t>180155</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>230950</t>
+          <t>229812</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4051,12 +4051,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>172141</t>
+          <t>172295</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>220852</t>
+          <t>221552</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>367984</t>
+          <t>368613</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>438470</t>
+          <t>436022</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>31,31%</t>
         </is>
       </c>
     </row>
@@ -4149,12 +4149,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>173694</t>
+          <t>176615</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>221503</t>
+          <t>223530</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>187893</t>
+          <t>186372</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>237718</t>
+          <t>236414</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>374434</t>
+          <t>373794</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>445749</t>
+          <t>443614</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>31,86%</t>
         </is>
       </c>
     </row>
@@ -4379,12 +4379,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>96170</t>
+          <t>91589</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>139390</t>
+          <t>135154</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4394,12 +4394,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>80769</t>
+          <t>80655</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>119213</t>
+          <t>121650</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>187617</t>
+          <t>184712</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>244310</t>
+          <t>245404</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,05%</t>
         </is>
       </c>
     </row>
@@ -4492,12 +4492,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>214543</t>
+          <t>214770</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>272334</t>
+          <t>271420</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4507,12 +4507,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>207012</t>
+          <t>207369</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>262337</t>
+          <t>264596</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4542,12 +4542,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>434919</t>
+          <t>435568</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>513986</t>
+          <t>516738</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4577,12 +4577,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>25,36%</t>
         </is>
       </c>
     </row>
@@ -4605,12 +4605,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>269108</t>
+          <t>271209</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>328836</t>
+          <t>333840</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4620,12 +4620,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>298515</t>
+          <t>297361</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>359232</t>
+          <t>359844</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>581050</t>
+          <t>582560</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>665234</t>
+          <t>671719</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4690,12 +4690,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>32,97%</t>
         </is>
       </c>
     </row>
@@ -4718,12 +4718,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>325752</t>
+          <t>328435</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>390558</t>
+          <t>390370</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>38,52%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>333776</t>
+          <t>331956</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>396865</t>
+          <t>394949</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4768,12 +4768,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>38,76%</t>
+          <t>38,58%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>678832</t>
+          <t>682816</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>773812</t>
+          <t>770833</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4803,12 +4803,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
+          <t>37,84%</t>
         </is>
       </c>
     </row>
@@ -4948,12 +4948,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>86077</t>
+          <t>85677</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>127025</t>
+          <t>128113</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4963,12 +4963,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>73403</t>
+          <t>75156</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>113354</t>
+          <t>113115</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4998,12 +4998,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>171755</t>
+          <t>171482</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>226476</t>
+          <t>227856</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5033,12 +5033,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,91%</t>
         </is>
       </c>
     </row>
@@ -5061,12 +5061,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>153461</t>
+          <t>151298</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>201948</t>
+          <t>201070</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5076,12 +5076,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>154984</t>
+          <t>153961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>205159</t>
+          <t>202960</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>317153</t>
+          <t>318855</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>387789</t>
+          <t>388686</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>25,43%</t>
         </is>
       </c>
     </row>
@@ -5174,12 +5174,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>181292</t>
+          <t>181641</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>231756</t>
+          <t>230470</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5189,12 +5189,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>196236</t>
+          <t>196341</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>247497</t>
+          <t>247972</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5224,12 +5224,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>390762</t>
+          <t>389044</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>465895</t>
+          <t>465073</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>30,42%</t>
         </is>
       </c>
     </row>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>239912</t>
+          <t>240680</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>293904</t>
+          <t>295341</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5302,12 +5302,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>39,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5322,12 +5322,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>257157</t>
+          <t>259068</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>314151</t>
+          <t>311437</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5337,12 +5337,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>40,54%</t>
+          <t>40,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5357,12 +5357,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>513563</t>
+          <t>510449</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>589780</t>
+          <t>588563</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5372,12 +5372,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>33,59%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>38,5%</t>
         </is>
       </c>
     </row>
@@ -5517,12 +5517,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>161119</t>
+          <t>162049</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>212083</t>
+          <t>212923</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>159492</t>
+          <t>157676</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>208753</t>
+          <t>208048</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5567,12 +5567,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5587,12 +5587,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>332068</t>
+          <t>332146</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>403464</t>
+          <t>399910</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5607,7 +5607,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,06%</t>
         </is>
       </c>
     </row>
@@ -5630,12 +5630,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>243776</t>
+          <t>241393</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>296278</t>
+          <t>295741</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5645,12 +5645,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5665,12 +5665,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>233410</t>
+          <t>229447</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>287908</t>
+          <t>290419</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5680,12 +5680,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5700,12 +5700,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>485831</t>
+          <t>489115</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>567502</t>
+          <t>572003</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5715,12 +5715,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>28,69%</t>
         </is>
       </c>
     </row>
@@ -5743,12 +5743,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>238720</t>
+          <t>240533</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>296467</t>
+          <t>295493</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5758,12 +5758,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5778,12 +5778,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>321757</t>
+          <t>317476</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>380823</t>
+          <t>382646</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5793,12 +5793,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5813,12 +5813,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>577080</t>
+          <t>576023</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>661410</t>
+          <t>659043</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5828,12 +5828,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>33,06%</t>
         </is>
       </c>
     </row>
@@ -5856,12 +5856,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>192222</t>
+          <t>194837</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>246612</t>
+          <t>246274</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5871,12 +5871,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5891,12 +5891,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>231078</t>
+          <t>232744</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>289587</t>
+          <t>288747</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5906,12 +5906,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5926,12 +5926,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>443013</t>
+          <t>442873</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>518506</t>
+          <t>520004</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>26,09%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>461391</t>
+          <t>460422</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>545609</t>
+          <t>543854</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>408884</t>
+          <t>412421</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>491952</t>
+          <t>498360</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>898156</t>
+          <t>893517</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1018361</t>
+          <t>1015518</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,61%</t>
         </is>
       </c>
     </row>
@@ -6199,12 +6199,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>832019</t>
+          <t>831442</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>936811</t>
+          <t>937451</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6214,12 +6214,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6234,12 +6234,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>817364</t>
+          <t>823384</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>922038</t>
+          <t>925922</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6249,12 +6249,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6269,12 +6269,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1682584</t>
+          <t>1682084</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1833247</t>
+          <t>1834579</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6289,7 +6289,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,39%</t>
         </is>
       </c>
     </row>
@@ -6312,12 +6312,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>921856</t>
+          <t>924252</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1031107</t>
+          <t>1030809</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6327,12 +6327,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6347,12 +6347,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1039514</t>
+          <t>1037399</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1153575</t>
+          <t>1152565</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6362,12 +6362,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6382,12 +6382,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1991839</t>
+          <t>1991373</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2155310</t>
+          <t>2154425</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6402,7 +6402,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>30,99%</t>
         </is>
       </c>
     </row>
@@ -6425,12 +6425,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>992066</t>
+          <t>988394</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1098336</t>
+          <t>1099963</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6440,82 +6440,82 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
+          <t>32,27%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>1031</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>1119928</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>1059267</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>1179250</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>31,61%</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>29,9%</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>33,29%</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>2163863</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t>2087027</t>
+        </is>
+      </c>
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t>2239782</t>
+        </is>
+      </c>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>31,13%</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>30,02%</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
           <t>32,22%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>1031</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>1119928</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>1061306</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>1178750</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>31,61%</t>
-        </is>
-      </c>
-      <c r="O27" s="2" t="inlineStr">
-        <is>
-          <t>29,96%</t>
-        </is>
-      </c>
-      <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t>33,27%</t>
-        </is>
-      </c>
-      <c r="Q27" s="2" t="inlineStr">
-        <is>
-          <t>2009</t>
-        </is>
-      </c>
-      <c r="R27" s="2" t="inlineStr">
-        <is>
-          <t>2163863</t>
-        </is>
-      </c>
-      <c r="S27" s="2" t="inlineStr">
-        <is>
-          <t>2081858</t>
-        </is>
-      </c>
-      <c r="T27" s="2" t="inlineStr">
-        <is>
-          <t>2243353</t>
-        </is>
-      </c>
-      <c r="U27" s="2" t="inlineStr">
-        <is>
-          <t>31,13%</t>
-        </is>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>29,95%</t>
-        </is>
-      </c>
-      <c r="W27" s="2" t="inlineStr">
-        <is>
-          <t>32,27%</t>
         </is>
       </c>
     </row>
@@ -6692,7 +6692,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según dificultad para llegar a fin de mes en 2016</t>
+          <t>Población según dificultad para llegar a fin de mes en 2016 (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6887,12 +6887,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>73933</t>
+          <t>72235</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>109600</t>
+          <t>109373</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6902,12 +6902,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>70519</t>
+          <t>70292</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>105280</t>
+          <t>105018</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6937,12 +6937,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>152567</t>
+          <t>153450</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>203064</t>
+          <t>202842</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6972,12 +6972,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,25%</t>
         </is>
       </c>
     </row>
@@ -7000,12 +7000,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>161441</t>
+          <t>159904</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>206205</t>
+          <t>206355</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7015,12 +7015,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7035,12 +7035,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>133384</t>
+          <t>133468</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>176649</t>
+          <t>176115</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7050,12 +7050,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7070,12 +7070,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>304210</t>
+          <t>304148</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>370694</t>
+          <t>366485</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7085,12 +7085,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>27,55%</t>
         </is>
       </c>
     </row>
@@ -7113,12 +7113,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>141520</t>
+          <t>142356</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>184088</t>
+          <t>187486</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7128,12 +7128,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7148,12 +7148,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>171916</t>
+          <t>171349</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>217156</t>
+          <t>218691</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7163,12 +7163,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7183,12 +7183,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>325980</t>
+          <t>323775</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>389601</t>
+          <t>390453</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7198,12 +7198,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,35%</t>
         </is>
       </c>
     </row>
@@ -7226,12 +7226,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>205667</t>
+          <t>206811</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>254169</t>
+          <t>258133</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>38,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>208444</t>
+          <t>206678</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>254652</t>
+          <t>255170</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7276,12 +7276,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>38,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>425477</t>
+          <t>429017</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>496354</t>
+          <t>499943</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7311,12 +7311,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>37,58%</t>
         </is>
       </c>
     </row>
@@ -7456,12 +7456,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>123255</t>
+          <t>122796</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>168904</t>
+          <t>166739</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7471,12 +7471,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>100894</t>
+          <t>100240</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>144361</t>
+          <t>145708</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7506,12 +7506,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>235691</t>
+          <t>236338</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>298276</t>
+          <t>300898</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7541,12 +7541,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,68%</t>
         </is>
       </c>
     </row>
@@ -7569,12 +7569,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>213835</t>
+          <t>213004</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>268791</t>
+          <t>268364</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7584,12 +7584,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>204031</t>
+          <t>208492</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>260060</t>
+          <t>259935</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>431938</t>
+          <t>430564</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>511058</t>
+          <t>506356</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>24,7%</t>
         </is>
       </c>
     </row>
@@ -7682,12 +7682,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>256038</t>
+          <t>255607</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>314274</t>
+          <t>312154</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7697,12 +7697,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7717,12 +7717,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>288747</t>
+          <t>287246</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>351261</t>
+          <t>347303</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>33,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>564478</t>
+          <t>560156</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>650164</t>
+          <t>645803</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>31,51%</t>
         </is>
       </c>
     </row>
@@ -7795,12 +7795,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>314360</t>
+          <t>313925</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>377033</t>
+          <t>378984</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7810,12 +7810,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>30,94%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>334175</t>
+          <t>330549</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>394881</t>
+          <t>392066</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>666165</t>
+          <t>663199</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>755539</t>
+          <t>750105</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>36,6%</t>
         </is>
       </c>
     </row>
@@ -8025,12 +8025,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>56701</t>
+          <t>55722</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>90491</t>
+          <t>87747</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8060,12 +8060,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>61338</t>
+          <t>61171</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>96275</t>
+          <t>97886</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>127123</t>
+          <t>124871</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>174091</t>
+          <t>175745</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,42%</t>
         </is>
       </c>
     </row>
@@ -8138,12 +8138,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>126489</t>
+          <t>126199</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>170271</t>
+          <t>172320</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8153,12 +8153,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8173,12 +8173,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>126811</t>
+          <t>127503</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>171052</t>
+          <t>172337</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>264815</t>
+          <t>265009</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>328698</t>
+          <t>329926</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,44%</t>
         </is>
       </c>
     </row>
@@ -8251,12 +8251,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>188374</t>
+          <t>188822</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>241050</t>
+          <t>244095</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8266,12 +8266,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8286,12 +8286,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>168828</t>
+          <t>172642</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>217161</t>
+          <t>220637</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8321,12 +8321,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>372657</t>
+          <t>371020</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>444923</t>
+          <t>443785</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>28,84%</t>
         </is>
       </c>
     </row>
@@ -8364,12 +8364,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>291498</t>
+          <t>290974</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>347702</t>
+          <t>348060</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8379,12 +8379,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>38,61%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>46,1%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8399,12 +8399,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>337374</t>
+          <t>336772</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>393864</t>
+          <t>393484</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>42,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>50,24%</t>
+          <t>50,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8434,12 +8434,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>644321</t>
+          <t>643005</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>722575</t>
+          <t>729322</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>41,87%</t>
+          <t>41,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>46,95%</t>
+          <t>47,39%</t>
         </is>
       </c>
     </row>
@@ -8594,12 +8594,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>174932</t>
+          <t>175657</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>225336</t>
+          <t>228980</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8609,12 +8609,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>176579</t>
+          <t>179294</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>230087</t>
+          <t>231909</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8644,12 +8644,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8664,12 +8664,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>369271</t>
+          <t>368718</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>441865</t>
+          <t>443287</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8679,12 +8679,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,44%</t>
         </is>
       </c>
     </row>
@@ -8707,12 +8707,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>226315</t>
+          <t>227181</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>283852</t>
+          <t>280598</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8722,12 +8722,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8742,12 +8742,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>210564</t>
+          <t>206397</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>265389</t>
+          <t>266960</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8757,12 +8757,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8777,12 +8777,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>451703</t>
+          <t>452505</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>533062</t>
+          <t>528819</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8792,12 +8792,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>26,77%</t>
         </is>
       </c>
     </row>
@@ -8820,12 +8820,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>223147</t>
+          <t>218088</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>275276</t>
+          <t>273784</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8855,12 +8855,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>271536</t>
+          <t>270537</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>330984</t>
+          <t>330401</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8870,12 +8870,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8890,12 +8890,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>510624</t>
+          <t>507986</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>591649</t>
+          <t>589535</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8905,12 +8905,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>29,85%</t>
         </is>
       </c>
     </row>
@@ -8933,12 +8933,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>205802</t>
+          <t>208081</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>259304</t>
+          <t>261068</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>270968</t>
+          <t>270746</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>331735</t>
+          <t>331726</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8983,7 +8983,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>493399</t>
+          <t>492717</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>575037</t>
+          <t>569818</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>28,85%</t>
         </is>
       </c>
     </row>
@@ -9163,12 +9163,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>464904</t>
+          <t>467671</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>548308</t>
+          <t>546607</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>450079</t>
+          <t>447698</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>533604</t>
+          <t>532598</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9213,12 +9213,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>933816</t>
+          <t>929363</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1063939</t>
+          <t>1054022</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9248,12 +9248,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,29%</t>
         </is>
       </c>
     </row>
@@ -9276,12 +9276,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>770659</t>
+          <t>777413</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>870229</t>
+          <t>877606</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9311,12 +9311,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>722181</t>
+          <t>718788</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>823397</t>
+          <t>817859</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9326,12 +9326,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9346,12 +9346,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1521820</t>
+          <t>1525099</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1665975</t>
+          <t>1669051</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9361,12 +9361,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,21%</t>
         </is>
       </c>
     </row>
@@ -9389,12 +9389,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>858093</t>
+          <t>851417</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>968504</t>
+          <t>963614</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9404,12 +9404,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>952591</t>
+          <t>951206</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1057504</t>
+          <t>1064047</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1834167</t>
+          <t>1841657</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1986832</t>
+          <t>1991019</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9474,12 +9474,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>28,88%</t>
         </is>
       </c>
     </row>
@@ -9502,12 +9502,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1075363</t>
+          <t>1069847</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1183427</t>
+          <t>1184093</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9517,12 +9517,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>35,16%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1203999</t>
+          <t>1198004</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1316227</t>
+          <t>1315886</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9552,12 +9552,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>37,31%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2308918</t>
+          <t>2314822</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2472259</t>
+          <t>2470344</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9587,12 +9587,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>35,83%</t>
         </is>
       </c>
     </row>
@@ -9769,7 +9769,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según dificultad para llegar a fin de mes en 2023</t>
+          <t>Población según dificultad para llegar a fin de mes en 2023 (tasa de respuesta: 98,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9964,12 +9964,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>123102</t>
+          <t>124077</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>167768</t>
+          <t>167165</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9979,12 +9979,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9999,12 +9999,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>159100</t>
+          <t>158698</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>313953</t>
+          <t>338052</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10014,12 +10014,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>47,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>304008</t>
+          <t>299375</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>492436</t>
+          <t>468309</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10049,12 +10049,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>35,2%</t>
         </is>
       </c>
     </row>
@@ -10077,12 +10077,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>179161</t>
+          <t>178664</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>225443</t>
+          <t>228384</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10092,12 +10092,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,52%</t>
+          <t>36,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>155925</t>
+          <t>151925</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>225989</t>
+          <t>226248</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10127,12 +10127,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>355143</t>
+          <t>352589</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>441028</t>
+          <t>436660</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10162,12 +10162,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>32,82%</t>
         </is>
       </c>
     </row>
@@ -10190,12 +10190,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>172052</t>
+          <t>173775</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>222614</t>
+          <t>226868</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10205,12 +10205,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>36,06%</t>
+          <t>36,75%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>158994</t>
+          <t>153112</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>223918</t>
+          <t>225236</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10240,12 +10240,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>341171</t>
+          <t>351106</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>432496</t>
+          <t>433030</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10275,12 +10275,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>32,55%</t>
         </is>
       </c>
     </row>
@@ -10303,12 +10303,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>56983</t>
+          <t>58071</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>90064</t>
+          <t>90163</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>86160</t>
+          <t>84682</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>125011</t>
+          <t>127233</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10353,12 +10353,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>154839</t>
+          <t>155323</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>206454</t>
+          <t>206250</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,5%</t>
         </is>
       </c>
     </row>
@@ -10533,12 +10533,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>117987</t>
+          <t>103840</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>298323</t>
+          <t>298040</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10548,12 +10548,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10568,12 +10568,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>178553</t>
+          <t>179450</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>224779</t>
+          <t>222268</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10583,12 +10583,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10603,12 +10603,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>279942</t>
+          <t>294599</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>492375</t>
+          <t>495610</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10618,12 +10618,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>23,24%</t>
         </is>
       </c>
     </row>
@@ -10646,12 +10646,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>195227</t>
+          <t>164988</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>443586</t>
+          <t>440124</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10661,12 +10661,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,55%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10681,12 +10681,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>282793</t>
+          <t>282871</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>332350</t>
+          <t>335490</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10696,12 +10696,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10716,12 +10716,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>412808</t>
+          <t>426888</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>749550</t>
+          <t>747258</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>35,05%</t>
         </is>
       </c>
     </row>
@@ -10759,12 +10759,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>317510</t>
+          <t>316932</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>786523</t>
+          <t>860723</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10774,12 +10774,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>66,58%</t>
+          <t>72,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>285945</t>
+          <t>286814</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>333581</t>
+          <t>335831</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10809,12 +10809,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>35,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>628527</t>
+          <t>626824</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1291455</t>
+          <t>1246305</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>60,57%</t>
+          <t>58,45%</t>
         </is>
       </c>
     </row>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>60927</t>
+          <t>49142</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>148984</t>
+          <t>146534</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10887,12 +10887,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>115366</t>
+          <t>115969</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>153560</t>
+          <t>153218</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10922,12 +10922,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>165551</t>
+          <t>163393</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>288033</t>
+          <t>289754</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10957,12 +10957,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,59%</t>
         </is>
       </c>
     </row>
@@ -11102,12 +11102,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>179750</t>
+          <t>178231</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>239223</t>
+          <t>236098</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11117,12 +11117,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>33,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>236949</t>
+          <t>235017</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>655659</t>
+          <t>636160</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11152,12 +11152,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,19%</t>
+          <t>71,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>441207</t>
+          <t>439964</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1027617</t>
+          <t>941679</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11187,12 +11187,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>64,4%</t>
+          <t>59,01%</t>
         </is>
       </c>
     </row>
@@ -11215,12 +11215,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>168344</t>
+          <t>169812</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>225883</t>
+          <t>225402</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11230,12 +11230,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>32,2%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>82948</t>
+          <t>83151</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>233414</t>
+          <t>232784</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -11265,12 +11265,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>213246</t>
+          <t>242088</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>438692</t>
+          <t>435578</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11300,12 +11300,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,3%</t>
         </is>
       </c>
     </row>
@@ -11328,12 +11328,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>170830</t>
+          <t>171011</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>231729</t>
+          <t>229467</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>32,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>105561</t>
+          <t>112679</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>283286</t>
+          <t>284441</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11378,12 +11378,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>250145</t>
+          <t>275110</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>487130</t>
+          <t>488678</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11413,12 +11413,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>30,62%</t>
         </is>
       </c>
     </row>
@@ -11441,12 +11441,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>76978</t>
+          <t>76375</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>120629</t>
+          <t>117753</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11456,12 +11456,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11476,12 +11476,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>54440</t>
+          <t>58466</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>160229</t>
+          <t>161549</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11491,12 +11491,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>131733</t>
+          <t>125974</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>255846</t>
+          <t>256120</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11526,12 +11526,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,05%</t>
         </is>
       </c>
     </row>
@@ -11671,12 +11671,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>287413</t>
+          <t>287946</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>350265</t>
+          <t>351805</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11686,12 +11686,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>38,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>222835</t>
+          <t>222625</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>313387</t>
+          <t>312623</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11721,12 +11721,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>28,84%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>534126</t>
+          <t>533020</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>645536</t>
+          <t>646331</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11756,12 +11756,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>32,3%</t>
         </is>
       </c>
     </row>
@@ -11784,12 +11784,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>225911</t>
+          <t>224111</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>287377</t>
+          <t>287134</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11799,12 +11799,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>229328</t>
+          <t>230151</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>315215</t>
+          <t>313118</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11834,12 +11834,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>476060</t>
+          <t>476588</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>584349</t>
+          <t>585199</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11869,12 +11869,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>29,24%</t>
         </is>
       </c>
     </row>
@@ -11897,12 +11897,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>182357</t>
+          <t>180535</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>237048</t>
+          <t>235948</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11912,12 +11912,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>215574</t>
+          <t>219139</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>302937</t>
+          <t>303456</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11947,12 +11947,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>425438</t>
+          <t>426682</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>522814</t>
+          <t>522054</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11982,12 +11982,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>26,09%</t>
         </is>
       </c>
     </row>
@@ -12010,12 +12010,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>115586</t>
+          <t>111344</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>163256</t>
+          <t>158649</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12025,12 +12025,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12045,12 +12045,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>181973</t>
+          <t>182900</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>410541</t>
+          <t>425367</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12060,12 +12060,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>39,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12080,12 +12080,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>316363</t>
+          <t>316729</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>567746</t>
+          <t>589047</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12095,12 +12095,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>29,43%</t>
         </is>
       </c>
     </row>
@@ -12240,12 +12240,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>702931</t>
+          <t>671908</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>986326</t>
+          <t>988667</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -12255,12 +12255,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -12275,12 +12275,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>894387</t>
+          <t>892697</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1578767</t>
+          <t>1571181</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12290,12 +12290,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>43,33%</t>
+          <t>43,12%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1749318</t>
+          <t>1756984</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2514046</t>
+          <t>2501249</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12325,12 +12325,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>35,43%</t>
         </is>
       </c>
     </row>
@@ -12353,12 +12353,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>758185</t>
+          <t>747140</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1092103</t>
+          <t>1094129</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12368,12 +12368,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>32,03%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>802919</t>
+          <t>793152</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1051387</t>
+          <t>1054558</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12403,12 +12403,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1685292</t>
+          <t>1690411</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2095617</t>
+          <t>2108261</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12438,12 +12438,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>29,86%</t>
         </is>
       </c>
     </row>
@@ -12466,12 +12466,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>913564</t>
+          <t>913485</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1666004</t>
+          <t>1674800</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12486,7 +12486,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>48,77%</t>
+          <t>49,03%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12501,12 +12501,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>803256</t>
+          <t>780196</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1077558</t>
+          <t>1079172</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12516,12 +12516,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12536,12 +12536,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1876756</t>
+          <t>1875373</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2679364</t>
+          <t>2730458</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12551,12 +12551,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>38,68%</t>
         </is>
       </c>
     </row>
@@ -12579,12 +12579,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>329674</t>
+          <t>317457</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>465813</t>
+          <t>466090</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12594,7 +12594,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -12614,12 +12614,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>518264</t>
+          <t>504971</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>809900</t>
+          <t>788405</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12629,12 +12629,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -12649,12 +12649,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>904865</t>
+          <t>894116</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1231268</t>
+          <t>1219741</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -12664,12 +12664,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,28%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P71_R2-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P71_R2-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>53061</t>
+          <t>54714</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>84509</t>
+          <t>86151</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>29112</t>
+          <t>28444</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>53450</t>
+          <t>51337</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>89613</t>
+          <t>89849</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>128959</t>
+          <t>128407</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,41%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>249808</t>
+          <t>251568</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>302119</t>
+          <t>303595</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,44%</t>
+          <t>36,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>44,07%</t>
+          <t>44,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>216003</t>
+          <t>215134</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>264359</t>
+          <t>264446</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,94%</t>
+          <t>38,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>479685</t>
+          <t>480703</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>553329</t>
+          <t>548976</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>35,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>40,23%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>216635</t>
+          <t>216564</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>266281</t>
+          <t>267479</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>38,84%</t>
+          <t>39,01%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>212471</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>260731</t>
+          <t>260198</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>38,4%</t>
+          <t>38,33%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>442304</t>
+          <t>445039</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>512855</t>
+          <t>511963</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>37,52%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>82842</t>
+          <t>82849</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>119751</t>
+          <t>119381</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>142535</t>
+          <t>140470</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>185126</t>
+          <t>186009</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>233075</t>
+          <t>235617</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>290758</t>
+          <t>292206</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,41%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>123975</t>
+          <t>124409</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>170202</t>
+          <t>172437</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>78038</t>
+          <t>77969</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>113959</t>
+          <t>116476</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>215689</t>
+          <t>213184</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>273253</t>
+          <t>275273</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,51%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>286635</t>
+          <t>289046</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>345626</t>
+          <t>348407</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>36,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>269737</t>
+          <t>268663</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>331439</t>
+          <t>327557</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>572088</t>
+          <t>569608</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>655166</t>
+          <t>654628</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>34,5%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>296527</t>
+          <t>293435</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>354443</t>
+          <t>354419</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>276857</t>
+          <t>278774</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>336673</t>
+          <t>336725</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>589912</t>
+          <t>591676</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>675764</t>
+          <t>675569</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>35,6%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>136600</t>
+          <t>135501</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>183634</t>
+          <t>182970</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>222076</t>
+          <t>224029</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>281405</t>
+          <t>280007</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>372894</t>
+          <t>371266</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>443565</t>
+          <t>445143</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,46%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>64966</t>
+          <t>65129</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>98737</t>
+          <t>101199</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>47251</t>
+          <t>46812</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>76379</t>
+          <t>74787</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>118906</t>
+          <t>118972</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>162278</t>
+          <t>162660</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,13%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>215738</t>
+          <t>214933</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>266523</t>
+          <t>265892</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>39,68%</t>
+          <t>39,59%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>153225</t>
+          <t>155507</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>196943</t>
+          <t>198263</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>384060</t>
+          <t>382234</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>449927</t>
+          <t>451127</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>33,56%</t>
+          <t>33,65%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>191928</t>
+          <t>193530</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>244248</t>
+          <t>244195</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>204097</t>
+          <t>203723</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>252545</t>
+          <t>253359</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,75%</t>
+          <t>37,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>412558</t>
+          <t>412649</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>479029</t>
+          <t>483442</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>36,06%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>110641</t>
+          <t>111596</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>154283</t>
+          <t>155899</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>182234</t>
+          <t>183048</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>227707</t>
+          <t>229099</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>34,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>306722</t>
+          <t>305097</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>371239</t>
+          <t>368526</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,49%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>129152</t>
+          <t>128048</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>172902</t>
+          <t>175919</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>124707</t>
+          <t>124516</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>168383</t>
+          <t>168873</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>267598</t>
+          <t>266342</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>329471</t>
+          <t>331096</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>17,04%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>263898</t>
+          <t>265646</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>319098</t>
+          <t>316114</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,68%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>251316</t>
+          <t>250927</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>308028</t>
+          <t>308108</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>531573</t>
+          <t>529911</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>608553</t>
+          <t>604980</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>31,14%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>265459</t>
+          <t>265429</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>320080</t>
+          <t>320575</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>34,61%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>261638</t>
+          <t>258096</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>320370</t>
+          <t>313509</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>540071</t>
+          <t>536103</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>618386</t>
+          <t>619889</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>31,9%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>170691</t>
+          <t>170973</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>220441</t>
+          <t>217708</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>273669</t>
+          <t>278025</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>333019</t>
+          <t>335016</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>32,95%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>461321</t>
+          <t>463418</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>533936</t>
+          <t>537936</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,69%</t>
         </is>
       </c>
     </row>
@@ -3009,12 +3009,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>411848</t>
+          <t>409375</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>492353</t>
+          <t>488228</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>304993</t>
+          <t>305740</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>376959</t>
+          <t>375145</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>734965</t>
+          <t>737235</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>841308</t>
+          <t>837968</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,8%</t>
         </is>
       </c>
     </row>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1063806</t>
+          <t>1070872</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1177014</t>
+          <t>1180516</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,12 +3137,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>33,15%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>940337</t>
+          <t>938744</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1046412</t>
+          <t>1040206</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2044277</t>
+          <t>2046099</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2191729</t>
+          <t>2190088</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>33,46%</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1020437</t>
+          <t>1025780</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1134335</t>
+          <t>1130703</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,12 +3250,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>35,0%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1002253</t>
+          <t>1002160</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1112961</t>
+          <t>1111829</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2052357</t>
+          <t>2058062</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2208030</t>
+          <t>2213543</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>33,82%</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>542936</t>
+          <t>539752</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>627470</t>
+          <t>628141</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>873730</t>
+          <t>872523</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>977973</t>
+          <t>974556</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1443179</t>
+          <t>1440326</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1577379</t>
+          <t>1578494</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,11%</t>
         </is>
       </c>
     </row>
@@ -3810,12 +3810,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>78772</t>
+          <t>80879</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>118723</t>
+          <t>120966</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3825,12 +3825,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3845,12 +3845,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>63195</t>
+          <t>62890</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>97390</t>
+          <t>98352</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3880,12 +3880,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>155203</t>
+          <t>154704</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>209283</t>
+          <t>208175</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>14,95%</t>
         </is>
       </c>
     </row>
@@ -3923,12 +3923,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>173596</t>
+          <t>170895</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>222099</t>
+          <t>220264</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3938,12 +3938,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3958,12 +3958,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>179891</t>
+          <t>181229</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>229531</t>
+          <t>228440</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>33,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>369864</t>
+          <t>367916</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>435864</t>
+          <t>437048</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>31,39%</t>
         </is>
       </c>
     </row>
@@ -4036,12 +4036,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>180155</t>
+          <t>179956</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>229812</t>
+          <t>230784</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4051,12 +4051,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,95%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>172295</t>
+          <t>175127</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>221552</t>
+          <t>224702</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>32,47%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>368613</t>
+          <t>366985</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>436022</t>
+          <t>434775</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>31,31%</t>
+          <t>31,22%</t>
         </is>
       </c>
     </row>
@@ -4149,12 +4149,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>176615</t>
+          <t>175097</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>223530</t>
+          <t>225716</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>186372</t>
+          <t>186229</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>236414</t>
+          <t>234470</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>33,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>373794</t>
+          <t>375864</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>443614</t>
+          <t>446157</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>32,04%</t>
         </is>
       </c>
     </row>
@@ -4379,12 +4379,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>91589</t>
+          <t>94816</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>135154</t>
+          <t>139174</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4394,82 +4394,82 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
+          <t>9,35%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>13,73%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>98795</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>80083</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>120299</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>9,65%</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>7,82%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>11,75%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>212786</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>184108</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>244586</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>10,44%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
           <t>9,04%</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>13,33%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>98795</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>80655</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>121650</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>9,65%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>7,88%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>11,88%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>212786</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>184712</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>245404</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>10,44%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>9,07%</t>
-        </is>
-      </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,01%</t>
         </is>
       </c>
     </row>
@@ -4492,12 +4492,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>214770</t>
+          <t>211357</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>271420</t>
+          <t>271472</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4507,7 +4507,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>207369</t>
+          <t>207284</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>264596</t>
+          <t>263687</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4542,12 +4542,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>435568</t>
+          <t>441289</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>516738</t>
+          <t>517031</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4577,12 +4577,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,38%</t>
         </is>
       </c>
     </row>
@@ -4605,12 +4605,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>271209</t>
+          <t>272010</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>333840</t>
+          <t>331122</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4620,12 +4620,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>32,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>297361</t>
+          <t>296614</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>359844</t>
+          <t>355526</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>34,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>582560</t>
+          <t>585568</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>671719</t>
+          <t>670964</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4690,12 +4690,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>32,93%</t>
         </is>
       </c>
     </row>
@@ -4718,12 +4718,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>328435</t>
+          <t>327452</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>390370</t>
+          <t>390675</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>38,52%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>331956</t>
+          <t>330629</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>394949</t>
+          <t>393212</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4768,12 +4768,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>682816</t>
+          <t>677763</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>770833</t>
+          <t>770871</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4803,7 +4803,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -4948,12 +4948,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>85677</t>
+          <t>86038</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>128113</t>
+          <t>130381</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4963,12 +4963,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>75156</t>
+          <t>76076</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>113115</t>
+          <t>113436</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4998,12 +4998,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>171482</t>
+          <t>174592</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>227856</t>
+          <t>229099</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5033,12 +5033,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,99%</t>
         </is>
       </c>
     </row>
@@ -5061,12 +5061,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>151298</t>
+          <t>153304</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>201070</t>
+          <t>200777</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5076,12 +5076,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>153961</t>
+          <t>153440</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>202960</t>
+          <t>202531</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>318855</t>
+          <t>320510</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>388686</t>
+          <t>391808</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,63%</t>
         </is>
       </c>
     </row>
@@ -5174,12 +5174,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>181641</t>
+          <t>180424</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>230470</t>
+          <t>236484</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5189,12 +5189,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>196341</t>
+          <t>195164</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>247972</t>
+          <t>246684</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5224,12 +5224,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>389044</t>
+          <t>389083</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>465073</t>
+          <t>462336</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>30,24%</t>
         </is>
       </c>
     </row>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>240680</t>
+          <t>240957</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>295341</t>
+          <t>295478</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5302,12 +5302,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>39,18%</t>
+          <t>39,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5322,12 +5322,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>259068</t>
+          <t>255960</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>311437</t>
+          <t>313652</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5337,12 +5337,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>40,19%</t>
+          <t>40,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5357,12 +5357,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>510449</t>
+          <t>517281</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>588563</t>
+          <t>591824</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5372,12 +5372,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>38,71%</t>
         </is>
       </c>
     </row>
@@ -5517,12 +5517,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>162049</t>
+          <t>158914</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>212923</t>
+          <t>207498</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>157676</t>
+          <t>157720</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>208048</t>
+          <t>205984</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5572,7 +5572,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5587,12 +5587,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>332146</t>
+          <t>331023</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>399910</t>
+          <t>401143</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5602,12 +5602,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>20,12%</t>
         </is>
       </c>
     </row>
@@ -5630,12 +5630,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>241393</t>
+          <t>240971</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>295741</t>
+          <t>297019</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5645,12 +5645,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5665,12 +5665,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>229447</t>
+          <t>233549</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>290419</t>
+          <t>287066</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5680,12 +5680,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5700,12 +5700,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>489115</t>
+          <t>486756</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>572003</t>
+          <t>567646</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5715,12 +5715,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,48%</t>
         </is>
       </c>
     </row>
@@ -5743,12 +5743,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240533</t>
+          <t>243237</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>295493</t>
+          <t>298837</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5758,12 +5758,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5778,12 +5778,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>317476</t>
+          <t>320317</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>382646</t>
+          <t>381161</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5793,12 +5793,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>36,24%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5813,12 +5813,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>576023</t>
+          <t>577654</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>659043</t>
+          <t>661958</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5828,12 +5828,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>33,21%</t>
         </is>
       </c>
     </row>
@@ -5856,12 +5856,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>194837</t>
+          <t>195797</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>246274</t>
+          <t>245562</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5871,12 +5871,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5891,12 +5891,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>232744</t>
+          <t>232821</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>288747</t>
+          <t>289687</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5926,12 +5926,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>442873</t>
+          <t>441226</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>520004</t>
+          <t>520429</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>26,11%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>460422</t>
+          <t>461112</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>543854</t>
+          <t>548972</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>412421</t>
+          <t>410620</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>498360</t>
+          <t>496460</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>893517</t>
+          <t>897974</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1015518</t>
+          <t>1021294</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,69%</t>
         </is>
       </c>
     </row>
@@ -6199,12 +6199,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>831442</t>
+          <t>831262</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>937451</t>
+          <t>938471</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6214,12 +6214,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6234,12 +6234,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>823384</t>
+          <t>823919</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>925922</t>
+          <t>928067</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6249,12 +6249,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6269,12 +6269,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1682084</t>
+          <t>1688701</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1834579</t>
+          <t>1841955</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6284,12 +6284,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,5%</t>
         </is>
       </c>
     </row>
@@ -6312,12 +6312,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>924252</t>
+          <t>923167</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1030809</t>
+          <t>1029402</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6327,12 +6327,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6347,12 +6347,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1037399</t>
+          <t>1037245</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1152565</t>
+          <t>1152151</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6367,7 +6367,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6382,12 +6382,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1991373</t>
+          <t>1984910</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2154425</t>
+          <t>2145600</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6397,12 +6397,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>30,86%</t>
         </is>
       </c>
     </row>
@@ -6425,12 +6425,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>988394</t>
+          <t>989070</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1099963</t>
+          <t>1096750</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6440,12 +6440,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>32,17%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6460,12 +6460,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1059267</t>
+          <t>1061488</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1179250</t>
+          <t>1178397</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>33,26%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6495,12 +6495,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2087027</t>
+          <t>2084308</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2239782</t>
+          <t>2246181</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>32,31%</t>
         </is>
       </c>
     </row>
@@ -6887,12 +6887,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>72235</t>
+          <t>73020</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>109373</t>
+          <t>108378</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6902,12 +6902,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>70292</t>
+          <t>70782</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>105018</t>
+          <t>105481</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6937,12 +6937,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>153450</t>
+          <t>150111</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>202842</t>
+          <t>201669</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6972,12 +6972,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,16%</t>
         </is>
       </c>
     </row>
@@ -7000,12 +7000,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>159904</t>
+          <t>158952</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>206355</t>
+          <t>205951</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7015,12 +7015,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7035,12 +7035,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>133468</t>
+          <t>133264</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>176115</t>
+          <t>178030</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7050,12 +7050,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7070,12 +7070,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>304148</t>
+          <t>306833</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>366485</t>
+          <t>366897</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7085,12 +7085,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,58%</t>
         </is>
       </c>
     </row>
@@ -7113,12 +7113,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>142356</t>
+          <t>141322</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>187486</t>
+          <t>185830</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7128,12 +7128,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7148,12 +7148,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>171349</t>
+          <t>171103</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>218691</t>
+          <t>215042</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7163,12 +7163,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7183,12 +7183,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>323775</t>
+          <t>325633</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>390453</t>
+          <t>389334</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7198,12 +7198,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>29,27%</t>
         </is>
       </c>
     </row>
@@ -7226,12 +7226,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>206811</t>
+          <t>206014</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>258133</t>
+          <t>255200</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>38,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>206678</t>
+          <t>204797</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>255170</t>
+          <t>253518</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7276,12 +7276,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>38,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>429017</t>
+          <t>426902</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>499943</t>
+          <t>494618</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7311,12 +7311,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>37,18%</t>
         </is>
       </c>
     </row>
@@ -7456,12 +7456,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>122796</t>
+          <t>121939</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>166739</t>
+          <t>169504</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7471,12 +7471,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>100240</t>
+          <t>101690</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>145708</t>
+          <t>142986</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7506,12 +7506,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>236338</t>
+          <t>236140</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>300898</t>
+          <t>296950</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7541,12 +7541,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,49%</t>
         </is>
       </c>
     </row>
@@ -7569,12 +7569,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>213004</t>
+          <t>210078</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>268364</t>
+          <t>264788</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7584,12 +7584,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>208492</t>
+          <t>204485</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>259935</t>
+          <t>256943</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>430564</t>
+          <t>434199</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>506356</t>
+          <t>514040</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>25,08%</t>
         </is>
       </c>
     </row>
@@ -7682,12 +7682,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>255607</t>
+          <t>255115</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>312154</t>
+          <t>313900</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7697,12 +7697,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>30,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7717,12 +7717,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>287246</t>
+          <t>288971</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>347303</t>
+          <t>350937</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>33,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>560156</t>
+          <t>562954</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>645803</t>
+          <t>647228</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,58%</t>
         </is>
       </c>
     </row>
@@ -7795,12 +7795,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>313925</t>
+          <t>312588</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>378984</t>
+          <t>377085</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7810,12 +7810,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>37,17%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>330549</t>
+          <t>335967</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>392066</t>
+          <t>396084</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>32,46%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>38,26%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>663199</t>
+          <t>668277</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>750105</t>
+          <t>756450</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>36,91%</t>
         </is>
       </c>
     </row>
@@ -8025,12 +8025,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>55722</t>
+          <t>57694</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>87747</t>
+          <t>90978</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8060,12 +8060,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>61171</t>
+          <t>60589</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>97886</t>
+          <t>94264</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>124871</t>
+          <t>128117</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>175745</t>
+          <t>174074</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,31%</t>
         </is>
       </c>
     </row>
@@ -8138,12 +8138,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>126199</t>
+          <t>124440</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>172320</t>
+          <t>172942</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8153,12 +8153,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8173,12 +8173,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>127503</t>
+          <t>126654</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>172337</t>
+          <t>169283</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>265009</t>
+          <t>267921</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>329926</t>
+          <t>332316</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,59%</t>
         </is>
       </c>
     </row>
@@ -8251,12 +8251,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>188822</t>
+          <t>191303</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>244095</t>
+          <t>242178</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8266,12 +8266,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8286,12 +8286,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>172642</t>
+          <t>169269</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>220637</t>
+          <t>219121</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8321,12 +8321,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>371020</t>
+          <t>376463</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>443785</t>
+          <t>442291</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>28,74%</t>
         </is>
       </c>
     </row>
@@ -8364,12 +8364,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>290974</t>
+          <t>291104</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>348060</t>
+          <t>347067</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8379,12 +8379,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>46,1%</t>
+          <t>45,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8399,12 +8399,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>336772</t>
+          <t>336568</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>393484</t>
+          <t>393440</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8414,7 +8414,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>42,96%</t>
+          <t>42,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -8434,12 +8434,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>643005</t>
+          <t>646278</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>729322</t>
+          <t>724896</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>41,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>47,39%</t>
+          <t>47,1%</t>
         </is>
       </c>
     </row>
@@ -8594,12 +8594,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>175657</t>
+          <t>177003</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>228980</t>
+          <t>226722</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8609,12 +8609,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>179294</t>
+          <t>177467</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>231909</t>
+          <t>234984</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8644,12 +8644,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8664,12 +8664,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>368718</t>
+          <t>370260</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>443287</t>
+          <t>442150</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8679,12 +8679,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,39%</t>
         </is>
       </c>
     </row>
@@ -8707,12 +8707,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>227181</t>
+          <t>226599</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>280598</t>
+          <t>280846</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8722,12 +8722,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8742,12 +8742,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>206397</t>
+          <t>210857</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>266960</t>
+          <t>263370</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8757,12 +8757,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8777,12 +8777,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>452505</t>
+          <t>454406</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>528819</t>
+          <t>532037</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8792,12 +8792,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,94%</t>
         </is>
       </c>
     </row>
@@ -8820,12 +8820,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>218088</t>
+          <t>220020</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>273784</t>
+          <t>274837</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8855,12 +8855,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>270537</t>
+          <t>273793</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>330401</t>
+          <t>332422</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8870,12 +8870,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8890,12 +8890,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>507986</t>
+          <t>510036</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>589535</t>
+          <t>590501</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8905,12 +8905,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>29,9%</t>
         </is>
       </c>
     </row>
@@ -8933,12 +8933,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>208081</t>
+          <t>204650</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>261068</t>
+          <t>257704</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>270746</t>
+          <t>272052</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>331726</t>
+          <t>333425</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8983,12 +8983,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>492717</t>
+          <t>492426</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>569818</t>
+          <t>573071</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>29,01%</t>
         </is>
       </c>
     </row>
@@ -9163,12 +9163,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>467671</t>
+          <t>465186</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>546607</t>
+          <t>551365</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9178,47 +9178,47 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
+          <t>13,81%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>16,37%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>455</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>489697</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>448441</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>538447</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
           <t>13,89%</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>16,23%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>455</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>489697</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>447698</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>532598</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>13,89%</t>
-        </is>
-      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>929363</t>
+          <t>941786</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1054022</t>
+          <t>1058084</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9248,12 +9248,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,35%</t>
         </is>
       </c>
     </row>
@@ -9276,12 +9276,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>777413</t>
+          <t>772346</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>877606</t>
+          <t>872085</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9311,12 +9311,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>718788</t>
+          <t>719559</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>817859</t>
+          <t>823848</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9326,12 +9326,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9346,12 +9346,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1525099</t>
+          <t>1528919</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1669051</t>
+          <t>1671297</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9361,12 +9361,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,24%</t>
         </is>
       </c>
     </row>
@@ -9389,12 +9389,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>851417</t>
+          <t>858785</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>963614</t>
+          <t>965855</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9404,12 +9404,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,68%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>951206</t>
+          <t>952309</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1064047</t>
+          <t>1062774</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1841657</t>
+          <t>1839872</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1991019</t>
+          <t>1986193</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9474,12 +9474,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>28,81%</t>
         </is>
       </c>
     </row>
@@ -9502,12 +9502,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1069847</t>
+          <t>1072306</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1184093</t>
+          <t>1181665</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9517,12 +9517,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1198004</t>
+          <t>1201964</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1315886</t>
+          <t>1319856</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9552,12 +9552,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>34,08%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>37,42%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2314822</t>
+          <t>2305668</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2470344</t>
+          <t>2468465</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9587,12 +9587,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>35,81%</t>
         </is>
       </c>
     </row>
@@ -9959,32 +9959,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>144822</t>
+          <t>162348</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>124077</t>
+          <t>138580</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>167165</t>
+          <t>187410</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9994,32 +9994,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>202702</t>
+          <t>166264</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>158698</t>
+          <t>148848</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>338052</t>
+          <t>188446</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,41%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10029,32 +10029,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>347524</t>
+          <t>328611</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>299375</t>
+          <t>300794</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>468309</t>
+          <t>360026</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>25,84%</t>
         </is>
       </c>
     </row>
@@ -10072,32 +10072,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>202484</t>
+          <t>215790</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>178664</t>
+          <t>191539</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>228384</t>
+          <t>243954</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>36,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10107,32 +10107,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>201406</t>
+          <t>215961</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>151925</t>
+          <t>193169</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>226248</t>
+          <t>234524</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10142,32 +10142,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>403889</t>
+          <t>431751</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>352589</t>
+          <t>400877</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>436660</t>
+          <t>467065</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>33,52%</t>
         </is>
       </c>
     </row>
@@ -10185,32 +10185,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>197560</t>
+          <t>205611</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>173775</t>
+          <t>180434</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>226868</t>
+          <t>229511</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -10220,32 +10220,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>200564</t>
+          <t>215629</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>153112</t>
+          <t>196744</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>225236</t>
+          <t>234660</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -10255,32 +10255,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>398124</t>
+          <t>421239</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>351106</t>
+          <t>390724</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>433030</t>
+          <t>454555</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>32,62%</t>
         </is>
       </c>
     </row>
@@ -10298,32 +10298,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>72479</t>
+          <t>88632</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>58071</t>
+          <t>71696</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>90163</t>
+          <t>106642</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10333,32 +10333,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>108418</t>
+          <t>123263</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>84682</t>
+          <t>107490</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>127233</t>
+          <t>140416</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10368,32 +10368,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>180896</t>
+          <t>211895</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>155323</t>
+          <t>189366</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>206250</t>
+          <t>243158</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>17,45%</t>
         </is>
       </c>
     </row>
@@ -10411,17 +10411,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>617345</t>
+          <t>672380</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>617345</t>
+          <t>672380</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>617345</t>
+          <t>672380</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10446,17 +10446,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>713090</t>
+          <t>721117</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>713090</t>
+          <t>721117</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>713090</t>
+          <t>721117</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10481,17 +10481,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1330434</t>
+          <t>1393496</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1330434</t>
+          <t>1393496</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1330434</t>
+          <t>1393496</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10528,32 +10528,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>225870</t>
+          <t>248074</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>103840</t>
+          <t>219201</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>298040</t>
+          <t>280234</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10563,32 +10563,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>200457</t>
+          <t>223339</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>179450</t>
+          <t>199428</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>222268</t>
+          <t>249951</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10598,32 +10598,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>426327</t>
+          <t>471414</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>294599</t>
+          <t>430805</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>495610</t>
+          <t>511363</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>24,36%</t>
         </is>
       </c>
     </row>
@@ -10641,32 +10641,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>340451</t>
+          <t>362240</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>164988</t>
+          <t>330921</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>440124</t>
+          <t>400639</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>38,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10676,32 +10676,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>307015</t>
+          <t>337442</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>282871</t>
+          <t>311939</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>335490</t>
+          <t>367759</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10711,32 +10711,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>647466</t>
+          <t>699682</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>426888</t>
+          <t>654487</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>747258</t>
+          <t>743108</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>33,33%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>35,4%</t>
         </is>
       </c>
     </row>
@@ -10754,32 +10754,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>504487</t>
+          <t>288750</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>316932</t>
+          <t>260465</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>860723</t>
+          <t>323727</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>72,86%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10789,22 +10789,22 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>309958</t>
+          <t>347859</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>286814</t>
+          <t>320748</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>335831</t>
+          <t>376457</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -10814,7 +10814,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>35,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10824,32 +10824,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>814445</t>
+          <t>636609</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>626824</t>
+          <t>594306</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1246305</t>
+          <t>679287</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>58,45%</t>
+          <t>32,36%</t>
         </is>
       </c>
     </row>
@@ -10867,32 +10867,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>110600</t>
+          <t>137277</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>49142</t>
+          <t>112657</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>146534</t>
+          <t>164423</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10902,32 +10902,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>133377</t>
+          <t>154389</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>115969</t>
+          <t>134437</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>153218</t>
+          <t>178459</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10937,32 +10937,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>243978</t>
+          <t>291665</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>163393</t>
+          <t>262785</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>289754</t>
+          <t>323269</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>15,4%</t>
         </is>
       </c>
     </row>
@@ -10980,17 +10980,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1181408</t>
+          <t>1036341</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1181408</t>
+          <t>1036341</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1181408</t>
+          <t>1036341</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11015,17 +11015,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>950807</t>
+          <t>1063029</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>950807</t>
+          <t>1063029</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>950807</t>
+          <t>1063029</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11050,17 +11050,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2132215</t>
+          <t>2099370</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2132215</t>
+          <t>2099370</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2132215</t>
+          <t>2099370</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11097,32 +11097,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>206793</t>
+          <t>239841</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>178231</t>
+          <t>212885</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>236098</t>
+          <t>269269</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>33,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11132,32 +11132,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>394166</t>
+          <t>216585</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>235017</t>
+          <t>192545</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>636160</t>
+          <t>238786</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,01%</t>
+          <t>29,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11167,32 +11167,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>600959</t>
+          <t>456426</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>439964</t>
+          <t>419126</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>941679</t>
+          <t>494861</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>59,01%</t>
+          <t>30,94%</t>
         </is>
       </c>
     </row>
@@ -11210,32 +11210,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>198125</t>
+          <t>212303</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>169812</t>
+          <t>184130</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>225402</t>
+          <t>244388</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -11245,32 +11245,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>172612</t>
+          <t>196991</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>83151</t>
+          <t>175334</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>232784</t>
+          <t>219970</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -11280,32 +11280,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>370737</t>
+          <t>409294</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>242088</t>
+          <t>371911</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>435578</t>
+          <t>443110</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,7%</t>
         </is>
       </c>
     </row>
@@ -11323,32 +11323,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>200267</t>
+          <t>231415</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>171011</t>
+          <t>202703</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>229467</t>
+          <t>262407</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11358,32 +11358,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>211719</t>
+          <t>252037</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>112679</t>
+          <t>227512</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>284441</t>
+          <t>277616</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11393,32 +11393,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>411986</t>
+          <t>483452</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>275110</t>
+          <t>447259</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>488678</t>
+          <t>523986</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>32,76%</t>
         </is>
       </c>
     </row>
@@ -11436,32 +11436,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>94741</t>
+          <t>110665</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>76375</t>
+          <t>88777</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>117753</t>
+          <t>135066</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11471,32 +11471,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>117366</t>
+          <t>139805</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>58466</t>
+          <t>120149</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>161549</t>
+          <t>159279</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11506,32 +11506,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>212107</t>
+          <t>250470</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>125974</t>
+          <t>221204</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>256120</t>
+          <t>283019</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>17,69%</t>
         </is>
       </c>
     </row>
@@ -11549,17 +11549,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>699926</t>
+          <t>794224</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>699926</t>
+          <t>794224</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>699926</t>
+          <t>794224</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11584,17 +11584,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>895863</t>
+          <t>805418</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>895863</t>
+          <t>805418</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>895863</t>
+          <t>805418</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11619,17 +11619,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1595789</t>
+          <t>1599642</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1595789</t>
+          <t>1599642</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1595789</t>
+          <t>1599642</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11666,32 +11666,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>318900</t>
+          <t>325666</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>287946</t>
+          <t>295825</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>351805</t>
+          <t>357421</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>34,77%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>36,53%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11701,32 +11701,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>280272</t>
+          <t>304157</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>222625</t>
+          <t>277768</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>312623</t>
+          <t>333394</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11736,32 +11736,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>599172</t>
+          <t>629823</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>533020</t>
+          <t>591225</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>646331</t>
+          <t>671757</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>32,2%</t>
         </is>
       </c>
     </row>
@@ -11779,32 +11779,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>253048</t>
+          <t>256147</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>224111</t>
+          <t>228075</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>287134</t>
+          <t>284462</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11814,32 +11814,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>283772</t>
+          <t>297247</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>230151</t>
+          <t>270929</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>313118</t>
+          <t>322674</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11849,32 +11849,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>536821</t>
+          <t>553394</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>476588</t>
+          <t>512599</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>585199</t>
+          <t>589767</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>28,27%</t>
         </is>
       </c>
     </row>
@@ -11892,32 +11892,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>208698</t>
+          <t>234361</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>180535</t>
+          <t>205406</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>235948</t>
+          <t>261637</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11927,32 +11927,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>271510</t>
+          <t>300325</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>219139</t>
+          <t>274254</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>303456</t>
+          <t>329136</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11962,32 +11962,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>480209</t>
+          <t>534686</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>426682</t>
+          <t>497682</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>522054</t>
+          <t>576547</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>27,64%</t>
         </is>
       </c>
     </row>
@@ -12005,32 +12005,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>136578</t>
+          <t>162165</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>111344</t>
+          <t>136833</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>158649</t>
+          <t>187657</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12040,32 +12040,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>248407</t>
+          <t>206123</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>182900</t>
+          <t>183956</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>425367</t>
+          <t>230857</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12075,32 +12075,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>384985</t>
+          <t>368289</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>316729</t>
+          <t>334558</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>589047</t>
+          <t>404231</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>19,38%</t>
         </is>
       </c>
     </row>
@@ -12118,17 +12118,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>917225</t>
+          <t>978339</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>917225</t>
+          <t>978339</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>917225</t>
+          <t>978339</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12153,17 +12153,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1083961</t>
+          <t>1107853</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1083961</t>
+          <t>1107853</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1083961</t>
+          <t>1107853</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12188,17 +12188,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2001187</t>
+          <t>2086192</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2001187</t>
+          <t>2086192</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2001187</t>
+          <t>2086192</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12235,32 +12235,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>896385</t>
+          <t>975929</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>671908</t>
+          <t>920845</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>988667</t>
+          <t>1041802</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -12270,32 +12270,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1077597</t>
+          <t>910345</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>892697</t>
+          <t>866828</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1571181</t>
+          <t>959181</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>43,12%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -12305,32 +12305,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1973982</t>
+          <t>1886274</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1756984</t>
+          <t>1813765</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2501249</t>
+          <t>1955684</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>27,24%</t>
         </is>
       </c>
     </row>
@@ -12348,32 +12348,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>994108</t>
+          <t>1046479</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>747140</t>
+          <t>987078</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1094129</t>
+          <t>1105526</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12383,32 +12383,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>964805</t>
+          <t>1047642</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>793152</t>
+          <t>1000701</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1054558</t>
+          <t>1097052</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>29,67%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12418,32 +12418,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1958913</t>
+          <t>2094121</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1690411</t>
+          <t>2016081</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2108261</t>
+          <t>2162438</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>30,12%</t>
         </is>
       </c>
     </row>
@@ -12461,32 +12461,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1111012</t>
+          <t>960137</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>913485</t>
+          <t>905425</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1674800</t>
+          <t>1020439</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>49,03%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12496,32 +12496,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>993752</t>
+          <t>1115849</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>780196</t>
+          <t>1064882</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1079172</t>
+          <t>1164462</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12531,32 +12531,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>2104764</t>
+          <t>2075986</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1875373</t>
+          <t>2002160</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2730458</t>
+          <t>2161599</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>30,11%</t>
         </is>
       </c>
     </row>
@@ -12574,32 +12574,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>414398</t>
+          <t>498739</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>317457</t>
+          <t>452722</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>466090</t>
+          <t>545741</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -12609,32 +12609,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>607568</t>
+          <t>623580</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>504971</t>
+          <t>581647</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>788405</t>
+          <t>665420</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -12644,32 +12644,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1021966</t>
+          <t>1122320</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>894116</t>
+          <t>1057634</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1219741</t>
+          <t>1186356</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>16,53%</t>
         </is>
       </c>
     </row>
@@ -12687,17 +12687,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>3415903</t>
+          <t>3481284</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3415903</t>
+          <t>3481284</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3415903</t>
+          <t>3481284</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12722,17 +12722,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>3643722</t>
+          <t>3697416</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3643722</t>
+          <t>3697416</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3643722</t>
+          <t>3697416</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12757,17 +12757,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>7059625</t>
+          <t>7178701</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>7059625</t>
+          <t>7178701</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>7059625</t>
+          <t>7178701</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
